--- a/expt/model.xlsx
+++ b/expt/model.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,6 +434,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Revenue (EUR)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Margin %</t>
         </is>
       </c>
@@ -450,6 +455,21 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Pasted FX</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>From Missing File 1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>From Missing File 2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>From Missing SharePoint</t>
         </is>
       </c>
     </row>
@@ -468,7 +488,11 @@
         <v/>
       </c>
       <c r="D2">
-        <f>B2/('[upstream_A.xlsx]Processed'!B2+'[upstream_A.xlsx]Processed'!C2)</f>
+        <f>'[upstream_A.xlsx]Processed'!D2</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>B2/(B2+C2)</f>
         <v/>
       </c>
       <c r="F2" t="n">
@@ -479,6 +503,18 @@
       </c>
       <c r="H2" t="n">
         <v>0.92</v>
+      </c>
+      <c r="J2">
+        <f>'[ghost_data.xlsx]Revenue'!A2*1.1</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>'[old_budget_2019.xlsx]Forecast'!B2</f>
+        <v/>
+      </c>
+      <c r="L2">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C2</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -496,7 +532,11 @@
         <v/>
       </c>
       <c r="D3">
-        <f>B3/('[upstream_A.xlsx]Processed'!B3+'[upstream_A.xlsx]Processed'!C3)</f>
+        <f>'[upstream_A.xlsx]Processed'!D3</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>B3/(B3+C3)</f>
         <v/>
       </c>
       <c r="F3" t="n">
@@ -507,6 +547,18 @@
       </c>
       <c r="H3" t="n">
         <v>0.91</v>
+      </c>
+      <c r="J3">
+        <f>'[ghost_data.xlsx]Revenue'!A3*1.1</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>'[old_budget_2019.xlsx]Forecast'!B3</f>
+        <v/>
+      </c>
+      <c r="L3">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -524,7 +576,11 @@
         <v/>
       </c>
       <c r="D4">
-        <f>B4/('[upstream_A.xlsx]Processed'!B4+'[upstream_A.xlsx]Processed'!C4)</f>
+        <f>'[upstream_A.xlsx]Processed'!D4</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>B4/(B4+C4)</f>
         <v/>
       </c>
       <c r="F4" t="n">
@@ -535,6 +591,18 @@
       </c>
       <c r="H4" t="n">
         <v>0.93</v>
+      </c>
+      <c r="J4">
+        <f>'[ghost_data.xlsx]Revenue'!A4*1.1</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>'[old_budget_2019.xlsx]Forecast'!B4</f>
+        <v/>
+      </c>
+      <c r="L4">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C4</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -552,7 +620,11 @@
         <v/>
       </c>
       <c r="D5">
-        <f>B5/('[upstream_A.xlsx]Processed'!B5+'[upstream_A.xlsx]Processed'!C5)</f>
+        <f>'[upstream_A.xlsx]Processed'!D5</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>B5/(B5+C5)</f>
         <v/>
       </c>
       <c r="F5" t="n">
@@ -563,6 +635,18 @@
       </c>
       <c r="H5" t="n">
         <v>0.9</v>
+      </c>
+      <c r="J5">
+        <f>'[ghost_data.xlsx]Revenue'!A5*1.1</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>'[old_budget_2019.xlsx]Forecast'!B5</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -580,7 +664,11 @@
         <v/>
       </c>
       <c r="D6">
-        <f>B6/('[upstream_A.xlsx]Processed'!B6+'[upstream_A.xlsx]Processed'!C6)</f>
+        <f>'[upstream_A.xlsx]Processed'!D6</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>B6/(B6+C6)</f>
         <v/>
       </c>
       <c r="F6" t="n">
@@ -591,6 +679,18 @@
       </c>
       <c r="H6" t="n">
         <v>0.89</v>
+      </c>
+      <c r="J6">
+        <f>'[ghost_data.xlsx]Revenue'!A6*1.1</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>'[old_budget_2019.xlsx]Forecast'!B6</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -608,7 +708,11 @@
         <v/>
       </c>
       <c r="D7">
-        <f>B7/('[upstream_A.xlsx]Processed'!B7+'[upstream_A.xlsx]Processed'!C7)</f>
+        <f>'[upstream_A.xlsx]Processed'!D7</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>B7/(B7+C7)</f>
         <v/>
       </c>
       <c r="F7" t="n">
@@ -619,6 +723,18 @@
       </c>
       <c r="H7" t="n">
         <v>0.88</v>
+      </c>
+      <c r="J7">
+        <f>'[ghost_data.xlsx]Revenue'!A7*1.1</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>'[old_budget_2019.xlsx]Forecast'!B7</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -636,7 +752,11 @@
         <v/>
       </c>
       <c r="D8">
-        <f>B8/('[upstream_A.xlsx]Processed'!B8+'[upstream_A.xlsx]Processed'!C8)</f>
+        <f>'[upstream_A.xlsx]Processed'!D8</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>B8/(B8+C8)</f>
         <v/>
       </c>
       <c r="F8" t="n">
@@ -647,6 +767,18 @@
       </c>
       <c r="H8" t="n">
         <v>0.91</v>
+      </c>
+      <c r="J8">
+        <f>'[ghost_data.xlsx]Revenue'!A8*1.1</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>'[old_budget_2019.xlsx]Forecast'!B8</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -664,7 +796,11 @@
         <v/>
       </c>
       <c r="D9">
-        <f>B9/('[upstream_A.xlsx]Processed'!B9+'[upstream_A.xlsx]Processed'!C9)</f>
+        <f>'[upstream_A.xlsx]Processed'!D9</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>B9/(B9+C9)</f>
         <v/>
       </c>
       <c r="F9" t="n">
@@ -675,6 +811,18 @@
       </c>
       <c r="H9" t="n">
         <v>0.9</v>
+      </c>
+      <c r="J9">
+        <f>'[ghost_data.xlsx]Revenue'!A9*1.1</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>'[old_budget_2019.xlsx]Forecast'!B9</f>
+        <v/>
+      </c>
+      <c r="L9">
+        <f>'https://corp.sharepoint.com/sites/finance/[quarterly_report.xlsx]Summary'!C9</f>
+        <v/>
       </c>
     </row>
   </sheetData>
